--- a/docentes/comercial/Sesiones de Teams · perfil comercial.xlsx
+++ b/docentes/comercial/Sesiones de Teams · perfil comercial.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18 reuniones · encuentros viernes de 7:30 a 9:00 a.m. · consultorio de 4:00 a 5:00 p.m. · cronograma ajustado del 15 de octubre de 2026</t>
+          <t>18 reuniones · encuentros viernes de 7:30 a 9:00 a.m. · consultorio de 4:00 a 5:00 p.m. · cronograma ajustado del 19 de octubre de 2026</t>
         </is>
       </c>
     </row>
